--- a/docs/requirement-traceability.xlsx
+++ b/docs/requirement-traceability.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>PIM Employee Id (numeric), Pay Grade Min/Max Salary</t>
+          <t>PIM Employee Id (numeric), Pay Grade Min/Max Salary, Personal Details Driver's License Number/License Expiry Date/Date of Birth (added via TC-PIM-006's expanded Personal Details coverage)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Employee List / Leave List / Candidate List filter dropdowns; Add Employee, Add User, Add Candidate form dropdowns</t>
+          <t>Employee List / Leave List / Candidate List filter dropdowns; Add Employee, Add User, Add Candidate form dropdowns; Personal Details Nationality/Marital Status and Custom Fields Blood Type dropdowns (added via TC-PIM-006/TC-PIM-013's expanded Personal Details coverage)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Recruitment Add Candidate (richest single form: text + dropdown + checkbox + file + date); PIM Add Employee; Admin Add User; Leave Apply</t>
+          <t>Recruitment Add Candidate (richest single form: text + dropdown + checkbox + file + date); PIM Add Employee (create) followed by Personal Details (edit - Driver's License, dates, dropdowns, radio, and a separate Custom Fields form, added via TC-PIM-006); Admin Add User; Leave Apply</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
